--- a/4p-index/STP_Decreto-37-1999_EIA-Decree_4P-Index.xlsx
+++ b/4p-index/STP_Decreto-37-1999_EIA-Decree_4P-Index.xlsx
@@ -636,12 +636,12 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.875</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>No explicit mention of 'plastics'; qualifies via Annex I items 8 (chemical/industrial manufacturing, potentially including plastics production/processing), 11 (hazardous waste) and 12 (municipal/industrial waste landfill, treatment and disposal — directly covers plastic waste streams) — plastics-relevance criteria (b)/(c). Screening (Art. 5) and the full EIA study (Art. 6) are combined into a single row per Rule 10, as they form one integrated mandatory assessment procedure.</t>
+          <t>Instrument type: Regulatory (1). No explicit mention of 'plastics'; qualifies via Annex I items 8 (chemical/industrial manufacturing, potentially including plastics production/processing), 11 (hazardous waste) and 12 (municipal/industrial waste landfill, treatment and disposal — directly covers plastic waste streams) — plastics-relevance criteria (b)/(c). Screening (Art. 5) and the full EIA study (Art. 6) are combined into a single row per Rule 10, as they form one integrated mandatory assessment procedure.</t>
         </is>
       </c>
     </row>
@@ -749,12 +749,12 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>0.20 (Governance &amp; coordination)</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>Applies to the same set of Annex-I-listed activities as Row 1, including plastics-relevant waste/industrial facilities; public hearings are discretionary depending on project scale (Art. 7.º(4)) — coded as a governance/participation instrument rather than Regulatory since it does not itself ban, standardise or economically incentivise anything.</t>
+          <t>Instrument type: Governance &amp; coordination (0.2). Applies to the same set of Annex-I-listed activities as Row 1, including plastics-relevant waste/industrial facilities; public hearings are discretionary depending on project scale (Art. 7.º(4)) — coded as a governance/participation instrument rather than Regulatory since it does not itself ban, standardise or economically incentivise anything.</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -897,12 +897,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>Functions as the core 'upstream gatekeeping' mechanism referenced in the policy summary — makes the environmental licence a legal precondition for all other sectoral licences, e.g. industrial operating licences for plastics-processing or packaging facilities.</t>
+          <t>Instrument type: Regulatory (1). Functions as the core 'upstream gatekeeping' mechanism referenced in the policy summary — makes the environmental licence a legal precondition for all other sectoral licences, e.g. industrial operating licences for plastics-processing or packaging facilities.</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.625</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>A sunset clause preventing indefinite 'banking' of unused environmental licences; relevant to plastics-processing or waste facilities that might otherwise hold a licence without updated impact data.</t>
+          <t>Instrument type: Regulatory (1). A sunset clause preventing indefinite 'banking' of unused environmental licences; relevant to plastics-processing or waste facilities that might otherwise hold a licence without updated impact data.</t>
         </is>
       </c>
     </row>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>Mixed governance (professional registry) and economic (registration fee, Annex III) instrument; scored as Regulatory (1.0) per Rule 10 because the core requirement — that only registered consultants may conduct EIA studies — is a mandatory professional/technical standard, with the fee treated as an ancillary economic component. Relevant to plastics only insofar as it underpins the quality/credibility of EIA studies for plastics-relevant facilities (criterion c).</t>
+          <t>Instrument type: Regulatory (1). Mixed governance (professional registry) and economic (registration fee, Annex III) instrument; scored as Regulatory (1.0) per Rule 10 because the core requirement — that only registered consultants may conduct EIA studies — is a mandatory professional/technical standard, with the fee treated as an ancillary economic component. Relevant to plastics only insofar as it underpins the quality/credibility of EIA studies for plastics-relevant facilities (criterion c).</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0.20 (Governance &amp; coordination)</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>Coded as a standalone governance/monitoring instrument (0.20) rather than folded into the Regulatory rows, consistent with Rule 11 (assignment of enforcement/monitoring responsibilities). Applies to any licensed or unlicensed activity capable of causing environmental damage, including plastics-relevant waste or industrial facilities.</t>
+          <t>Instrument type: Governance &amp; coordination (0.2). Coded as a standalone governance/monitoring instrument (0.20) rather than folded into the Regulatory rows, consistent with Rule 11 (assignment of enforcement/monitoring responsibilities). Applies to any licensed or unlicensed activity capable of causing environmental damage, including plastics-relevant waste or industrial facilities.</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1 (Regulatory)</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>Directly enforces the EIA/licensing gatekeeping regime (Rows 1 and 3) against non-compliant proponents, including those operating plastics-processing, packaging or waste-treatment facilities without required EIA clearance. Mixed instrument: mandatory liability (in force) combined with a discretionary embargo enabling power — coded S = 1 overall because the liability rule itself uses mandatory language; flagged here as a borderline case.</t>
+          <t>Instrument type: Regulatory (1). Directly enforces the EIA/licensing gatekeeping regime (Rows 1 and 3) against non-compliant proponents, including those operating plastics-processing, packaging or waste-treatment facilities without required EIA clearance. Mixed instrument: mandatory liability (in force) combined with a discretionary embargo enabling power — coded S = 1 overall because the liability rule itself uses mandatory language; flagged here as a borderline case.</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0.60 (Economic)</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>[auto]</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>Ring-fenced/self-generated funding: fees are explicitly earmarked to finance the EIA process itself (Annex II(3); same wording in Annex III(3) for consultant registration fees) — this underpins policy-level Col M = 1. Applies to any project subject to EIA (including plastics-relevant facilities under Annex I), calculated as a percentage of project value rather than as a plastics-specific levy.</t>
+          <t>Instrument type: Economic (0.6). Ring-fenced/self-generated funding: fees are explicitly earmarked to finance the EIA process itself (Annex II(3); same wording in Annex III(3) for consultant registration fees) — this underpins policy-level Col M = 1. Applies to any project subject to EIA (including plastics-relevant facilities under Annex I), calculated as a percentage of project value rather than as a plastics-specific levy.</t>
         </is>
       </c>
     </row>

--- a/4p-index/STP_Decreto-37-1999_EIA-Decree_4P-Index.xlsx
+++ b/4p-index/STP_Decreto-37-1999_EIA-Decree_4P-Index.xlsx
@@ -588,61 +588,47 @@
           <t>Implements Lei n.º 10/1999 (Basic Environmental Law) by establishing a mandatory prior Environmental Impact Assessment (EIA) and environmental licensing process for projects and activities likely to cause significant environmental impacts — including pollutant emissions, solid/hazardous waste generation and disposal, construction-material and mineral extraction, and industrial/chemical facilities. Contains no explicit mention of 'plastics', but functions as an upstream gatekeeping tool directly relevant to plastic-processing, packaging or waste-treatment facilities, since Annex I lists industrial/chemical installations and municipal/industrial waste landfill, treatment and disposal facilities as activities requiring EIA.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Executive decree ('Decreto') approved by the Council of Ministers — 'Visto e aprovado pelo conselho de Ministro em S. Tomé, aos 25 de Fevereiro de 1999' / 'Seen and approved by the Council of Ministers in São Tomé, on 25 February 1999' — and promulgated by the President of the Republic on 3 August 1999, issued under Article 99(c) of the Constitution as a regulation implementing Lei n.º 10/1999. It is a sub-legislative executive instrument, not an Act passed by the National Assembly.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>agriculture, forestry, water, energy, oil &amp; gas, mining, industry, chemicals, construction/infrastructure, transport, waste management, fisheries, health, tourism</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K2" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>production, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.' (Same wording repeated in Annex III(3) for environmental-consultant registration fees.) Fee schedule (Annex II(1)-(2)): up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex III: consultant registration fees of USD 150 (individual) / USD 1,000 (firms).</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O2" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -654,25 +640,19 @@
           <t>Art. 2.º: 'Todas as actividades que pela sua natureza, dimensão ou localização sejam susceptíveis de provocar impactos significativos no ambiente deverão submeter a sua realização ao processo de avaliação de impacto ambiental nos termos do presente diploma legal.' / 'All activities which, by their nature, size or location, are liable to cause significant impacts on the environment must submit their execution to the environmental impact assessment process under the terms of this decree.' Art. 5.º(1): mandatory 'pré-avaliação' (screening) for all activities listed in Annex I. Annex I includes, inter alia: item 8 'Instalações e complexos industriais e agro-industriais destinados ao fabrico de cimento, coque, produtos químicos, pesticida e siderúrgicos' / 'Industrial and agro-industrial installations and complexes for the manufacture of cement, coke, chemical products, pesticides and steel products'; item 11 'Transporte, processamento e eliminação de resíduos tóxicos e perigosos inclusive radioactivos' / 'Transport, processing and disposal of toxic and hazardous waste, including radioactive waste'; item 12 'Aterro, tratamento e eliminação de lixo municipal, industrial e hospitalar' / 'Landfilling, treatment and disposal of municipal, industrial and hospital waste'. Art. 6.º(1): the full EIA study and monitoring programme are entirely the responsibility of the proponent.</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Art. 3.º: responsible authority designated — 'compete à entidade governamental responsável pela gestão do ambiente' / 'it is incumbent upon the government entity responsible for environmental management' (+0.25 authority). Art. 18.º: mandatory regular inspection and supervision (+0.25 monitoring). Art. 19.º(1): proponents who fail to submit to the EIA/licensing process 'responderá civil e criminalmente pelas consequências e/ou danos que causar ao ambiente' / 'shall be held civilly and criminally liable for the consequences and/or damage caused to the environment' (+0.25 enforcement). Not unconditional: Art. 5.º(5): 'Ficam isentas da realização do estudo do impacto ambiental as propostas de actividades que vierem fazer face a situação de emergência derivadas de desastre ou calamidade natural.' / 'Proposals for activities addressing an emergency arising from a natural disaster or calamity are exempt from carrying out the environmental impact study' (explicit exemption — 0).</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
+      <c r="V2" s="2" t="n">
+        <v>0.875</v>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
@@ -701,61 +681,47 @@
           <t>Implements Lei n.º 10/1999 (Basic Environmental Law) by establishing a mandatory prior Environmental Impact Assessment (EIA) and environmental licensing process for projects and activities likely to cause significant environmental impacts — including pollutant emissions, solid/hazardous waste generation and disposal, construction-material and mineral extraction, and industrial/chemical facilities. Contains no explicit mention of 'plastics', but functions as an upstream gatekeeping tool directly relevant to plastic-processing, packaging or waste-treatment facilities, since Annex I lists industrial/chemical installations and municipal/industrial waste landfill, treatment and disposal facilities as activities requiring EIA.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Executive decree ('Decreto') approved by the Council of Ministers — 'Visto e aprovado pelo conselho de Ministro em S. Tomé, aos 25 de Fevereiro de 1999' / 'Seen and approved by the Council of Ministers in São Tomé, on 25 February 1999' — and promulgated by the President of the Republic on 3 August 1999, issued under Article 99(c) of the Constitution as a regulation implementing Lei n.º 10/1999. It is a sub-legislative executive instrument, not an Act passed by the National Assembly.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>agriculture, forestry, water, energy, oil &amp; gas, mining, industry, chemicals, construction/infrastructure, transport, waste management, fisheries, health, tourism</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K3" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>production, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.' (Same wording repeated in Annex III(3) for environmental-consultant registration fees.) Fee schedule (Annex II(1)-(2)): up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex III: consultant registration fees of USD 150 (individual) / USD 1,000 (firms).</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O3" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -767,25 +733,19 @@
           <t>Art. 7.º(1)-(2): the responsible entity must adopt consultation methods ensuring public access to information; the consultation period 'deverá ser amplamente... divulgado' / 'must be widely publicised', and the period for submissions must not exceed 30 working days. Art. 7.º(3): the proponent must deposit four copies of the non-technical summary of the EIA study with the responsible entity and the District Chamber ('Câmara Distrital') for public consultation. Art. 7.º(8): a final consultation report must record the proceedings, participation, and responses to all issues raised.</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Authority designated: entidade governamental responsável pela gestão do ambiente (+0.25). Documentation/monitoring: Art. 7.º(8) mandatory final report on the consultation process (+0.25). No specific fine for consultation failures is set out (0 enforcement). Not unconditional: Art. 7.º(4): public hearings are convened only 'sempre que a dimensão ou efeitos previsíveis do projecto justifiquem' / 'whenever the size or foreseeable effects of the project justify it' (0).</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="V3" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
@@ -814,61 +774,47 @@
           <t>Implements Lei n.º 10/1999 (Basic Environmental Law) by establishing a mandatory prior Environmental Impact Assessment (EIA) and environmental licensing process for projects and activities likely to cause significant environmental impacts — including pollutant emissions, solid/hazardous waste generation and disposal, construction-material and mineral extraction, and industrial/chemical facilities. Contains no explicit mention of 'plastics', but functions as an upstream gatekeeping tool directly relevant to plastic-processing, packaging or waste-treatment facilities, since Annex I lists industrial/chemical installations and municipal/industrial waste landfill, treatment and disposal facilities as activities requiring EIA.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Executive decree ('Decreto') approved by the Council of Ministers — 'Visto e aprovado pelo conselho de Ministro em S. Tomé, aos 25 de Fevereiro de 1999' / 'Seen and approved by the Council of Ministers in São Tomé, on 25 February 1999' — and promulgated by the President of the Republic on 3 August 1999, issued under Article 99(c) of the Constitution as a regulation implementing Lei n.º 10/1999. It is a sub-legislative executive instrument, not an Act passed by the National Assembly.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>agriculture, forestry, water, energy, oil &amp; gas, mining, industry, chemicals, construction/infrastructure, transport, waste management, fisheries, health, tourism</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K4" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>production, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.' (Same wording repeated in Annex III(3) for environmental-consultant registration fees.) Fee schedule (Annex II(1)-(2)): up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex III: consultant registration fees of USD 150 (individual) / USD 1,000 (firms).</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O4" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
@@ -880,25 +826,19 @@
           <t>Art. 10.º(1): 'Quando seja comprovada a viabilidade ambiental das actividades propostas, será emitida uma licença ambiental para a actividade proposta.' / 'Once the environmental viability of the proposed activities has been demonstrated, an environmental licence shall be issued for the proposed activity.' Art. 13.º(1): 'A emissão das licenças ambientais precede a das demais licenças legalmente exigidas para cada actividade.' / 'The issuance of environmental licences precedes that of any other licences legally required for each activity.' Art. 13.º(3): 'As demais licenças exigidas por lei para cada caso, só serão emitidas mediante a comprovação do pedido de publicidade da licença ambiental no Diário da República.' / 'Other licences required by law for each case shall only be issued upon proof that the environmental licence has been submitted for publication in the Official Gazette.'</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Authority designated (entidade governamental responsável) (+0.25). Enforcement: tied to Art. 19.º sanctions for proceeding without the required licence (+0.25). Monitoring/verification: Art. 13.º(3) requires proof of publication of the environmental licence before any other licence is issued — a documented verification step (+0.25). Unconditional: no exemptions are stated for this precedence rule (+0.25).</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="V4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
@@ -927,61 +867,47 @@
           <t>Implements Lei n.º 10/1999 (Basic Environmental Law) by establishing a mandatory prior Environmental Impact Assessment (EIA) and environmental licensing process for projects and activities likely to cause significant environmental impacts — including pollutant emissions, solid/hazardous waste generation and disposal, construction-material and mineral extraction, and industrial/chemical facilities. Contains no explicit mention of 'plastics', but functions as an upstream gatekeeping tool directly relevant to plastic-processing, packaging or waste-treatment facilities, since Annex I lists industrial/chemical installations and municipal/industrial waste landfill, treatment and disposal facilities as activities requiring EIA.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Executive decree ('Decreto') approved by the Council of Ministers — 'Visto e aprovado pelo conselho de Ministro em S. Tomé, aos 25 de Fevereiro de 1999' / 'Seen and approved by the Council of Ministers in São Tomé, on 25 February 1999' — and promulgated by the President of the Republic on 3 August 1999, issued under Article 99(c) of the Constitution as a regulation implementing Lei n.º 10/1999. It is a sub-legislative executive instrument, not an Act passed by the National Assembly.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>agriculture, forestry, water, energy, oil &amp; gas, mining, industry, chemicals, construction/infrastructure, transport, waste management, fisheries, health, tourism</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K5" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>production, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.' (Same wording repeated in Annex III(3) for environmental-consultant registration fees.) Fee schedule (Annex II(1)-(2)): up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex III: consultant registration fees of USD 150 (individual) / USD 1,000 (firms).</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O5" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
@@ -993,25 +919,19 @@
           <t>Art. 14.º(1): 'Será considerada caducada e de nenhum efeito toda a licença cuja actividade não seja implementada nos dois anos seguintes à sua emissão.' / 'Any licence whose activity has not been implemented within the two years following its issuance shall be considered lapsed and of no effect.' Art. 14.º(2): the proponent must apply for an extension, and the responsible entity may either (a) revalidate the licence if still considered valid, or (b) require a full or partial update of the EIA study.</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
+      <c r="S5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0.25</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
           <t>Authority designated to decide on renewal/updating (+0.25 authority). No enforcement penalty specified for operating on a lapsed licence beyond the general Art. 19 regime (0, not evidenced within this article). No monitoring/tracking mechanism for expiry specified (0). Not unconditional: renewal outcome is discretionary/conditional on the responsible entity's decision (0).</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0.625</t>
-        </is>
+      <c r="V5" s="2" t="n">
+        <v>0.625</v>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
@@ -1040,61 +960,47 @@
           <t>Implements Lei n.º 10/1999 (Basic Environmental Law) by establishing a mandatory prior Environmental Impact Assessment (EIA) and environmental licensing process for projects and activities likely to cause significant environmental impacts — including pollutant emissions, solid/hazardous waste generation and disposal, construction-material and mineral extraction, and industrial/chemical facilities. Contains no explicit mention of 'plastics', but functions as an upstream gatekeeping tool directly relevant to plastic-processing, packaging or waste-treatment facilities, since Annex I lists industrial/chemical installations and municipal/industrial waste landfill, treatment and disposal facilities as activities requiring EIA.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Executive decree ('Decreto') approved by the Council of Ministers — 'Visto e aprovado pelo conselho de Ministro em S. Tomé, aos 25 de Fevereiro de 1999' / 'Seen and approved by the Council of Ministers in São Tomé, on 25 February 1999' — and promulgated by the President of the Republic on 3 August 1999, issued under Article 99(c) of the Constitution as a regulation implementing Lei n.º 10/1999. It is a sub-legislative executive instrument, not an Act passed by the National Assembly.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>agriculture, forestry, water, energy, oil &amp; gas, mining, industry, chemicals, construction/infrastructure, transport, waste management, fisheries, health, tourism</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K6" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>production, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.' (Same wording repeated in Annex III(3) for environmental-consultant registration fees.) Fee schedule (Annex II(1)-(2)): up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex III: consultant registration fees of USD 150 (individual) / USD 1,000 (firms).</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O6" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
@@ -1106,25 +1012,19 @@
           <t>Art. 15.º(1)-(2): the responsible entity shall create a registration system for environmental consultants; 'Só poderão realizar estudos de impacto ambiental, em São Tomé e Príncipe, os técnicos... registados como consultores.' / 'Only technicians... registered as consultants may carry out environmental impact studies in São Tomé and Príncipe.' Art. 16.º(1)-(2): registration certificates are valid for five years, automatically renewable, and may be annulled for false or misleading information. Art. 17.º: registered consultants are civilly and criminally liable for the information they provide in EIA reports. Annex III: registration fees of USD 150 (individual) / USD 1,000 (firms), used to finance the EIA process.</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="S6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>Authority designated (entidade governamental responsável creates and administers the registry) (+0.25). Enforcement: Art. 16.º(2) annulment of registration for false information; Art. 17.º civil/criminal liability of consultants (+0.25). Monitoring: Art. 15.º(4) requires qualification certificates and curriculum vitae as part of the registration/verification process (+0.25). Unconditional: no exemptions are stated to the registration requirement itself (+0.25).</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="V6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
@@ -1153,61 +1053,47 @@
           <t>Implements Lei n.º 10/1999 (Basic Environmental Law) by establishing a mandatory prior Environmental Impact Assessment (EIA) and environmental licensing process for projects and activities likely to cause significant environmental impacts — including pollutant emissions, solid/hazardous waste generation and disposal, construction-material and mineral extraction, and industrial/chemical facilities. Contains no explicit mention of 'plastics', but functions as an upstream gatekeeping tool directly relevant to plastic-processing, packaging or waste-treatment facilities, since Annex I lists industrial/chemical installations and municipal/industrial waste landfill, treatment and disposal facilities as activities requiring EIA.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Executive decree ('Decreto') approved by the Council of Ministers — 'Visto e aprovado pelo conselho de Ministro em S. Tomé, aos 25 de Fevereiro de 1999' / 'Seen and approved by the Council of Ministers in São Tomé, on 25 February 1999' — and promulgated by the President of the Republic on 3 August 1999, issued under Article 99(c) of the Constitution as a regulation implementing Lei n.º 10/1999. It is a sub-legislative executive instrument, not an Act passed by the National Assembly.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>agriculture, forestry, water, energy, oil &amp; gas, mining, industry, chemicals, construction/infrastructure, transport, waste management, fisheries, health, tourism</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K7" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>production, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.' (Same wording repeated in Annex III(3) for environmental-consultant registration fees.) Fee schedule (Annex II(1)-(2)): up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex III: consultant registration fees of USD 150 (individual) / USD 1,000 (firms).</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0.74</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O7" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
@@ -1219,25 +1105,19 @@
           <t>Art. 18.º(1): 'A entidade governamental responsável pela gestão ambiental deverá proceder com regularidade à inspecção e fiscalização das actividades de monitoramento levadas a cabo pelo proponente com vista a garantir a qualidade do ambiente.' / 'The government entity responsible for environmental management must regularly inspect and supervise the monitoring activities carried out by the proponent, in order to guarantee environmental quality.' Art. 18.º(2): the responsible entity may order environmental audits of ongoing activities that were not subject to the EIA process and that could cause environmental damage. Art. 18.º(3): environmental audits shall be subject to specific regulation.</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>Authority designated (+0.25). This article itself establishes the mandatory regular inspection/audit mechanism (+0.25 monitoring). No specific fines are set out within this article for inspection failures (0 enforcement — general sanctions are in Art. 19.º, coded separately). Not unconditional: the audit power for already-ongoing, non-assessed activities is discretionary ('poderá ordenar'), and audit procedures are deferred to a future specific regulation not yet identified (Art. 18.º(3)) (0).</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="V7" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
@@ -1266,61 +1146,47 @@
           <t>Implements Lei n.º 10/1999 (Basic Environmental Law) by establishing a mandatory prior Environmental Impact Assessment (EIA) and environmental licensing process for projects and activities likely to cause significant environmental impacts — including pollutant emissions, solid/hazardous waste generation and disposal, construction-material and mineral extraction, and industrial/chemical facilities. Contains no explicit mention of 'plastics', but functions as an upstream gatekeeping tool directly relevant to plastic-processing, packaging or waste-treatment facilities, since Annex I lists industrial/chemical installations and municipal/industrial waste landfill, treatment and disposal facilities as activities requiring EIA.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="G8" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Executive decree ('Decreto') approved by the Council of Ministers — 'Visto e aprovado pelo conselho de Ministro em S. Tomé, aos 25 de Fevereiro de 1999' / 'Seen and approved by the Council of Ministers in São Tomé, on 25 February 1999' — and promulgated by the President of the Republic on 3 August 1999, issued under Article 99(c) of the Constitution as a regulation implementing Lei n.º 10/1999. It is a sub-legislative executive instrument, not an Act passed by the National Assembly.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>agriculture, forestry, water, energy, oil &amp; gas, mining, industry, chemicals, construction/infrastructure, transport, waste management, fisheries, health, tourism</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K8" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>production, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.' (Same wording repeated in Annex III(3) for environmental-consultant registration fees.) Fee schedule (Annex II(1)-(2)): up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex III: consultant registration fees of USD 150 (individual) / USD 1,000 (firms).</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O8" s="2" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
@@ -1332,25 +1198,19 @@
           <t>Art. 19.º(1): 'Qualquer proponente que a revelia da entidade governamental responsável pela gestão do ambiente, não submeter o seu projecto ou actividade ao processo prévio de licenciamento ambiental... ou que... altere substancialmente o projecto inicial sem submeter as alterações a novo estudo ou ainda que não implemente as medidas propostas no estudo ou na licença ambiental responderá civil e criminalmente pelas consequências e/ou danos que causar ao ambiente.' / 'Any proponent who, without the knowledge of the government entity responsible for environmental management, fails to submit its project or activity to the prior environmental licensing process... or who substantially alters the initial project without submitting the changes to a new study, or who fails to implement the measures proposed in the study or in the environmental licence, shall be held civilly and criminally liable for the consequences and/or damage caused to the environment.' Art. 19.º(2): the responsible entity, jointly with the licensing authority, may embargo the project, prohibiting the proponent from continuing any activity until the EIA process is completed and licence conditions are met.</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
           <t>Authority designated — joint action of the entidade governamental responsável and the entidade licenciadora (+0.25). This article itself is the enforcement/liability provision (civil and criminal liability, plus embargo power) (+0.25 enforcement). No monitoring mechanism specified within this article (relies on Art. 18.º, coded separately) (0). Not unconditional: the embargo power is discretionary ('poderá... embargar') (0).</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="V8" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
@@ -1379,61 +1239,47 @@
           <t>Implements Lei n.º 10/1999 (Basic Environmental Law) by establishing a mandatory prior Environmental Impact Assessment (EIA) and environmental licensing process for projects and activities likely to cause significant environmental impacts — including pollutant emissions, solid/hazardous waste generation and disposal, construction-material and mineral extraction, and industrial/chemical facilities. Contains no explicit mention of 'plastics', but functions as an upstream gatekeeping tool directly relevant to plastic-processing, packaging or waste-treatment facilities, since Annex I lists industrial/chemical installations and municipal/industrial waste landfill, treatment and disposal facilities as activities requiring EIA.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="G9" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Executive decree ('Decreto') approved by the Council of Ministers — 'Visto e aprovado pelo conselho de Ministro em S. Tomé, aos 25 de Fevereiro de 1999' / 'Seen and approved by the Council of Ministers in São Tomé, on 25 February 1999' — and promulgated by the President of the Republic on 3 August 1999, issued under Article 99(c) of the Constitution as a regulation implementing Lei n.º 10/1999. It is a sub-legislative executive instrument, not an Act passed by the National Assembly.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>agriculture, forestry, water, energy, oil &amp; gas, mining, industry, chemicals, construction/infrastructure, transport, waste management, fisheries, health, tourism</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="K9" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>production, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.' (Same wording repeated in Annex III(3) for environmental-consultant registration fees.) Fee schedule (Annex II(1)-(2)): up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex III: consultant registration fees of USD 150 (individual) / USD 1,000 (firms).</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O9" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
@@ -1445,25 +1291,19 @@
           <t>Annex II: 'Taxas a pagar pelo proponente pelo processo de revisão do estudo de impacto e emissão da licença ambiental' / 'Fees payable by the proponent for the process of reviewing the impact study and issuing the environmental licence'. Fee schedule: up to USD 500,000 project value — 1% of project value or a minimum of USD 1,000; above USD 500,000 — USD 5,000 plus 0.5% of the value exceeding USD 500,000, capped at USD 50,000. Annex II(3): 'As taxas pagas ao abrigo do presente diploma serão utilizadas para financiar o processo de avaliação do impacto ambiental nos termos do artigo 10.º.' / 'Fees paid under this decree shall be used to finance the environmental impact assessment process under the terms of Article 10.'</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
           <t>Authority implied (fees are payable to, and the EIA process financed by, the entidade governamental responsável) (+0.25 authority). No explicit penalty for non-payment is mentioned (0 enforcement). No monitoring mechanism specified for fee collection (0). Unconditional: the fee schedule and caps are set out with no stated exemptions (+0.25).</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="V9" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
